--- a/reports/cme9yo328000h9qwgg1fm0gid/2025/07/template___________________________07_2025.xlsx
+++ b/reports/cme9yo328000h9qwgg1fm0gid/2025/07/template___________________________07_2025.xlsx
@@ -85,7 +85,43 @@
     <t>Напомена:</t>
   </si>
   <si>
-    <t>Наплаћен износ у prepaid саобраћају у јулу периоду</t>
+    <r>
+      <t xml:space="preserve">Наплаћен износ у </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <charset val="238"/>
+        <color rgb="FF000000"/>
+        <family val="2"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>prepost</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <charset val="238"/>
+        <color rgb="FF000000"/>
+        <family val="2"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="238"/>
+        <color rgb="FF000000"/>
+        <family val="2"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">саобраћају у периоду </t>
+    </r>
   </si>
   <si>
     <t>01.07.2025 do 31.07.2025</t>
@@ -839,7 +875,7 @@
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
